--- a/Configs/GameConfig/Datas/skill.xlsx
+++ b/Configs/GameConfig/Datas/skill.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R63a1269a40024093"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd3cb621def5741e4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -338,47 +338,35 @@
         <x:v>resName</x:v>
       </x:c>
       <x:c r="D1" t="str">
-        <x:v>name</x:v>
+        <x:v>category</x:v>
       </x:c>
       <x:c r="E1" t="str">
-        <x:v>category</x:v>
+        <x:v>rangeTiles</x:v>
       </x:c>
       <x:c r="F1" t="str">
-        <x:v>description</x:v>
+        <x:v>cooldownSeconds</x:v>
       </x:c>
       <x:c r="G1" t="str">
-        <x:v>healthMultiplier</x:v>
+        <x:v>handlerKey</x:v>
       </x:c>
       <x:c r="H1" t="str">
-        <x:v>speed</x:v>
+        <x:v>effectBuffId</x:v>
       </x:c>
       <x:c r="I1" t="str">
-        <x:v>rangeTiles</x:v>
+        <x:v>effectDurationMs</x:v>
       </x:c>
       <x:c r="J1" t="str">
-        <x:v>cooldownSeconds</x:v>
+        <x:v>triggerAttackCount</x:v>
       </x:c>
       <x:c r="K1" t="str">
-        <x:v>source</x:v>
-      </x:c>
-      <x:c r="L1" t="str">
-        <x:v>confidence</x:v>
-      </x:c>
-      <x:c r="M1" t="str">
-        <x:v>handlerKey</x:v>
-      </x:c>
-      <x:c r="N1" t="str">
-        <x:v>effectBuffId</x:v>
-      </x:c>
-      <x:c r="O1" t="str">
-        <x:v>effectDurationMs</x:v>
-      </x:c>
-      <x:c r="P1" t="str">
-        <x:v>triggerAttackCount</x:v>
-      </x:c>
-      <x:c r="Q1" t="str">
         <x:v>effectDamageMultiplier</x:v>
       </x:c>
+      <x:c r="L1"/>
+      <x:c r="M1"/>
+      <x:c r="N1"/>
+      <x:c r="O1"/>
+      <x:c r="P1"/>
+      <x:c r="Q1"/>
     </x:row>
     <x:row r="2">
       <x:c r="A2" t="str">
@@ -394,44 +382,32 @@
         <x:v>string</x:v>
       </x:c>
       <x:c r="E2" t="str">
+        <x:v>float?</x:v>
+      </x:c>
+      <x:c r="F2" t="str">
+        <x:v>int?</x:v>
+      </x:c>
+      <x:c r="G2" t="str">
         <x:v>string</x:v>
-      </x:c>
-      <x:c r="F2" t="str">
-        <x:v>string</x:v>
-      </x:c>
-      <x:c r="G2" t="str">
-        <x:v>int?</x:v>
       </x:c>
       <x:c r="H2" t="str">
         <x:v>int?</x:v>
       </x:c>
       <x:c r="I2" t="str">
-        <x:v>float?</x:v>
+        <x:v>int?</x:v>
       </x:c>
       <x:c r="J2" t="str">
         <x:v>int?</x:v>
       </x:c>
       <x:c r="K2" t="str">
-        <x:v>string</x:v>
-      </x:c>
-      <x:c r="L2" t="str">
-        <x:v>string?</x:v>
-      </x:c>
-      <x:c r="M2" t="str">
-        <x:v>string</x:v>
-      </x:c>
-      <x:c r="N2" t="str">
-        <x:v>int?</x:v>
-      </x:c>
-      <x:c r="O2" t="str">
-        <x:v>int?</x:v>
-      </x:c>
-      <x:c r="P2" t="str">
-        <x:v>int?</x:v>
-      </x:c>
-      <x:c r="Q2" t="str">
         <x:v>float?</x:v>
       </x:c>
+      <x:c r="L2"/>
+      <x:c r="M2"/>
+      <x:c r="N2"/>
+      <x:c r="O2"/>
+      <x:c r="P2"/>
+      <x:c r="Q2"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" t="str">
@@ -459,53 +435,41 @@
         <x:v>##</x:v>
       </x:c>
       <x:c r="B4" t="str">
-        <x:v>ID(主键)</x:v>
+        <x:v>主键，技能唯一 ID</x:v>
       </x:c>
       <x:c r="C4" t="str">
-        <x:v>资源名(原主键)</x:v>
+        <x:v>资源名，原主键</x:v>
       </x:c>
       <x:c r="D4" t="str">
-        <x:v>名称</x:v>
+        <x:v>类别，只能填 active / boss / passive</x:v>
       </x:c>
       <x:c r="E4" t="str">
-        <x:v>类别</x:v>
+        <x:v>作用范围格数，只被特定 Handler 解释</x:v>
       </x:c>
       <x:c r="F4" t="str">
-        <x:v>描述</x:v>
+        <x:v>冷却秒数，必须填写且不能为负</x:v>
       </x:c>
       <x:c r="G4" t="str">
-        <x:v>血量倍数</x:v>
+        <x:v>代码处理器注册键，不能为空，必须由程序确认已注册</x:v>
       </x:c>
       <x:c r="H4" t="str">
-        <x:v>速度</x:v>
+        <x:v>效果 Buff ID，引用 buff.Id</x:v>
       </x:c>
       <x:c r="I4" t="str">
-        <x:v>范围(格)</x:v>
+        <x:v>Buff/效果持续毫秒</x:v>
       </x:c>
       <x:c r="J4" t="str">
-        <x:v>冷却(秒)</x:v>
+        <x:v>累计多少次普通攻击后触发主动技能</x:v>
       </x:c>
       <x:c r="K4" t="str">
-        <x:v>源码标记</x:v>
-      </x:c>
-      <x:c r="L4" t="str">
-        <x:v>置信度</x:v>
-      </x:c>
-      <x:c r="M4" t="str">
-        <x:v>技能处理器键</x:v>
-      </x:c>
-      <x:c r="N4" t="str">
-        <x:v>效果Buff ID(可空)</x:v>
-      </x:c>
-      <x:c r="O4" t="str">
-        <x:v>效果持续毫秒(可空)</x:v>
-      </x:c>
-      <x:c r="P4" t="str">
-        <x:v>触发攻击计数</x:v>
-      </x:c>
-      <x:c r="Q4" t="str">
-        <x:v>单箭伤害倍率</x:v>
-      </x:c>
+        <x:v>单箭伤害倍率，如火箭每箭倍率</x:v>
+      </x:c>
+      <x:c r="L4"/>
+      <x:c r="M4"/>
+      <x:c r="N4"/>
+      <x:c r="O4"/>
+      <x:c r="P4"/>
+      <x:c r="Q4"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5"/>
@@ -516,27 +480,21 @@
         <x:v>LeapSlash</x:v>
       </x:c>
       <x:c r="D5" t="str">
-        <x:v>跳斩</x:v>
-      </x:c>
-      <x:c r="E5" t="str">
         <x:v>active</x:v>
       </x:c>
-      <x:c r="F5" t="str">
-        <x:v>接下来数次攻击为跳斩，每次攻击对周围造成50％溅射伤害</x:v>
-      </x:c>
-      <x:c r="G5"/>
+      <x:c r="E5"/>
+      <x:c r="F5" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G5" t="str">
+        <x:v>LeapSlash</x:v>
+      </x:c>
       <x:c r="H5"/>
       <x:c r="I5"/>
-      <x:c r="J5" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K5" t="str">
-        <x:v>38497</x:v>
-      </x:c>
+      <x:c r="J5"/>
+      <x:c r="K5"/>
       <x:c r="L5"/>
-      <x:c r="M5" t="str">
-        <x:v>LeapSlash</x:v>
-      </x:c>
+      <x:c r="M5"/>
       <x:c r="N5"/>
       <x:c r="O5"/>
       <x:c r="P5"/>
@@ -551,27 +509,21 @@
         <x:v>SevenInSevenOut</x:v>
       </x:c>
       <x:c r="D6" t="str">
-        <x:v>七进七出</x:v>
-      </x:c>
-      <x:c r="E6" t="str">
         <x:v>active</x:v>
       </x:c>
-      <x:c r="F6" t="str">
-        <x:v>释放一个幻象冲进敌群，以乱刺状态来回突进七次</x:v>
-      </x:c>
-      <x:c r="G6"/>
+      <x:c r="E6"/>
+      <x:c r="F6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G6" t="str">
+        <x:v>SevenInSevenOut</x:v>
+      </x:c>
       <x:c r="H6"/>
       <x:c r="I6"/>
-      <x:c r="J6" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K6" t="str">
-        <x:v>45655</x:v>
-      </x:c>
+      <x:c r="J6"/>
+      <x:c r="K6"/>
       <x:c r="L6"/>
-      <x:c r="M6" t="str">
-        <x:v>SevenInSevenOut</x:v>
-      </x:c>
+      <x:c r="M6"/>
       <x:c r="N6"/>
       <x:c r="O6"/>
       <x:c r="P6"/>
@@ -586,38 +538,32 @@
         <x:v>BattleShout</x:v>
       </x:c>
       <x:c r="D7" t="str">
-        <x:v>大喝</x:v>
-      </x:c>
-      <x:c r="E7" t="str">
         <x:v>active</x:v>
       </x:c>
-      <x:c r="F7" t="str">
-        <x:v>大喝一声，砸晕一圈敌人，晕眩2秒</x:v>
-      </x:c>
-      <x:c r="G7"/>
-      <x:c r="H7"/>
+      <x:c r="E7" t="n">
+        <x:v>3.5</x:v>
+      </x:c>
+      <x:c r="F7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G7" t="str">
+        <x:v>BattleShout</x:v>
+      </x:c>
+      <x:c r="H7" t="n">
+        <x:v>9</x:v>
+      </x:c>
       <x:c r="I7" t="n">
-        <x:v>3.5</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="J7" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K7" t="str">
-        <x:v>45659</x:v>
-      </x:c>
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="K7"/>
       <x:c r="L7"/>
-      <x:c r="M7" t="str">
-        <x:v>BattleShout</x:v>
-      </x:c>
-      <x:c r="N7" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="O7" t="n">
-        <x:v>2000</x:v>
-      </x:c>
-      <x:c r="P7" t="n">
-        <x:v>15</x:v>
-      </x:c>
+      <x:c r="M7"/>
+      <x:c r="N7"/>
+      <x:c r="O7"/>
+      <x:c r="P7"/>
       <x:c r="Q7"/>
     </x:row>
     <x:row r="8">
@@ -629,27 +575,21 @@
         <x:v>HolySword</x:v>
       </x:c>
       <x:c r="D8" t="str">
-        <x:v>圣剑</x:v>
-      </x:c>
-      <x:c r="E8" t="str">
         <x:v>active</x:v>
       </x:c>
-      <x:c r="F8" t="str">
-        <x:v>释放一柄圣剑，造成范围伤害并击倒敌人</x:v>
-      </x:c>
-      <x:c r="G8"/>
+      <x:c r="E8"/>
+      <x:c r="F8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G8" t="str">
+        <x:v>HolySword</x:v>
+      </x:c>
       <x:c r="H8"/>
       <x:c r="I8"/>
-      <x:c r="J8" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K8" t="str">
-        <x:v>45902</x:v>
-      </x:c>
+      <x:c r="J8"/>
+      <x:c r="K8"/>
       <x:c r="L8"/>
-      <x:c r="M8" t="str">
-        <x:v>HolySword</x:v>
-      </x:c>
+      <x:c r="M8"/>
       <x:c r="N8"/>
       <x:c r="O8"/>
       <x:c r="P8"/>
@@ -664,27 +604,21 @@
         <x:v>ArrowRain</x:v>
       </x:c>
       <x:c r="D9" t="str">
-        <x:v>箭雨</x:v>
-      </x:c>
-      <x:c r="E9" t="str">
         <x:v>active</x:v>
       </x:c>
-      <x:c r="F9" t="str">
-        <x:v>射出大量箭雨</x:v>
-      </x:c>
-      <x:c r="G9"/>
+      <x:c r="E9"/>
+      <x:c r="F9" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G9" t="str">
+        <x:v>ArrowRain</x:v>
+      </x:c>
       <x:c r="H9"/>
       <x:c r="I9"/>
-      <x:c r="J9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K9" t="str">
-        <x:v>46141</x:v>
-      </x:c>
+      <x:c r="J9"/>
+      <x:c r="K9"/>
       <x:c r="L9"/>
-      <x:c r="M9" t="str">
-        <x:v>ArrowRain</x:v>
-      </x:c>
+      <x:c r="M9"/>
       <x:c r="N9"/>
       <x:c r="O9"/>
       <x:c r="P9"/>
@@ -699,37 +633,31 @@
         <x:v>FireArrowBarrage</x:v>
       </x:c>
       <x:c r="D10" t="str">
-        <x:v>火箭烈</x:v>
-      </x:c>
-      <x:c r="E10" t="str">
         <x:v>active</x:v>
       </x:c>
-      <x:c r="F10" t="str">
-        <x:v>射出大量火箭轰炸敌人</x:v>
-      </x:c>
-      <x:c r="G10"/>
+      <x:c r="E10" t="n">
+        <x:v>5.5</x:v>
+      </x:c>
+      <x:c r="F10" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G10" t="str">
+        <x:v>FireArrowBarrage</x:v>
+      </x:c>
       <x:c r="H10"/>
-      <x:c r="I10" t="n">
-        <x:v>5.5</x:v>
-      </x:c>
+      <x:c r="I10"/>
       <x:c r="J10" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K10" t="str">
-        <x:v>46145</x:v>
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="K10" t="n">
+        <x:v>2</x:v>
       </x:c>
       <x:c r="L10"/>
-      <x:c r="M10" t="str">
-        <x:v>FireArrowBarrage</x:v>
-      </x:c>
+      <x:c r="M10"/>
       <x:c r="N10"/>
       <x:c r="O10"/>
-      <x:c r="P10" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="Q10" t="n">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="P10"/>
+      <x:c r="Q10"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11"/>
@@ -740,27 +668,21 @@
         <x:v>StunPassive</x:v>
       </x:c>
       <x:c r="D11" t="str">
-        <x:v>晕眩</x:v>
-      </x:c>
-      <x:c r="E11" t="str">
         <x:v>passive</x:v>
       </x:c>
-      <x:c r="F11" t="str">
-        <x:v>每次攻击概率造成敌人眩晕</x:v>
-      </x:c>
-      <x:c r="G11"/>
+      <x:c r="E11"/>
+      <x:c r="F11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G11" t="str">
+        <x:v>StunPassive</x:v>
+      </x:c>
       <x:c r="H11"/>
       <x:c r="I11"/>
-      <x:c r="J11" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K11" t="str">
-        <x:v>46279</x:v>
-      </x:c>
+      <x:c r="J11"/>
+      <x:c r="K11"/>
       <x:c r="L11"/>
-      <x:c r="M11" t="str">
-        <x:v>StunPassive</x:v>
-      </x:c>
+      <x:c r="M11"/>
       <x:c r="N11"/>
       <x:c r="O11"/>
       <x:c r="P11"/>
@@ -775,39 +697,29 @@
         <x:v>SoulCapture</x:v>
       </x:c>
       <x:c r="D12" t="str">
-        <x:v>摄魂</x:v>
+        <x:v>boss</x:v>
       </x:c>
       <x:c r="E12" t="str">
-        <x:v>boss</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F12" t="str">
-        <x:v>使我方小兵陷入混乱，无法攻击</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="G12" t="str">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="H12" t="str">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="I12" t="str">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="J12" t="str">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="K12" t="str">
-        <x:v>12054</x:v>
-      </x:c>
+        <x:v>SoulCapture</x:v>
+      </x:c>
+      <x:c r="H12" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="I12" t="n">
+        <x:v>2000</x:v>
+      </x:c>
+      <x:c r="J12"/>
+      <x:c r="K12"/>
       <x:c r="L12"/>
-      <x:c r="M12" t="str">
-        <x:v>SoulCapture</x:v>
-      </x:c>
-      <x:c r="N12" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="O12" t="n">
-        <x:v>2000</x:v>
-      </x:c>
+      <x:c r="M12"/>
+      <x:c r="N12"/>
+      <x:c r="O12"/>
       <x:c r="P12"/>
       <x:c r="Q12"/>
     </x:row>
@@ -820,33 +732,23 @@
         <x:v>SoulSummon</x:v>
       </x:c>
       <x:c r="D13" t="str">
-        <x:v>招魂</x:v>
+        <x:v>boss</x:v>
       </x:c>
       <x:c r="E13" t="str">
-        <x:v>boss</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F13" t="str">
-        <x:v>做法复活死亡的小兵</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="G13" t="str">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="H13" t="str">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="I13" t="str">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="J13" t="str">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="K13" t="str">
-        <x:v>12062</x:v>
-      </x:c>
+        <x:v>SoulSummon</x:v>
+      </x:c>
+      <x:c r="H13"/>
+      <x:c r="I13"/>
+      <x:c r="J13"/>
+      <x:c r="K13"/>
       <x:c r="L13"/>
-      <x:c r="M13" t="str">
-        <x:v>SoulSummon</x:v>
-      </x:c>
+      <x:c r="M13"/>
       <x:c r="N13"/>
       <x:c r="O13"/>
       <x:c r="P13"/>
@@ -861,35 +763,23 @@
         <x:v>Inspire</x:v>
       </x:c>
       <x:c r="D14" t="str">
-        <x:v>鼓舞</x:v>
+        <x:v>boss</x:v>
       </x:c>
       <x:c r="E14" t="str">
-        <x:v>boss</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F14" t="str">
-        <x:v>激励身边单位，大幅提升血量和移速</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="G14" t="str">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="H14" t="str">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="I14" t="str">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="J14" t="str">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="K14" t="str">
-        <x:v>12070</x:v>
-      </x:c>
-      <x:c r="L14" t="str">
-        <x:v>INFERRED_HEALTH_MULTIPLIER</x:v>
-      </x:c>
-      <x:c r="M14" t="str">
         <x:v>Inspire</x:v>
       </x:c>
+      <x:c r="H14"/>
+      <x:c r="I14"/>
+      <x:c r="J14"/>
+      <x:c r="K14"/>
+      <x:c r="L14"/>
+      <x:c r="M14"/>
       <x:c r="N14"/>
       <x:c r="O14"/>
       <x:c r="P14"/>
@@ -904,33 +794,23 @@
         <x:v>Demolition</x:v>
       </x:c>
       <x:c r="D15" t="str">
-        <x:v>拆迁</x:v>
+        <x:v>boss</x:v>
       </x:c>
       <x:c r="E15" t="str">
-        <x:v>boss</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F15" t="str">
-        <x:v>将空白地块转化为不可用</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="G15" t="str">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="H15" t="str">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="I15" t="str">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="J15" t="str">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="K15" t="str">
-        <x:v>12078</x:v>
-      </x:c>
+        <x:v>Demolition</x:v>
+      </x:c>
+      <x:c r="H15"/>
+      <x:c r="I15"/>
+      <x:c r="J15"/>
+      <x:c r="K15"/>
       <x:c r="L15"/>
-      <x:c r="M15" t="str">
-        <x:v>Demolition</x:v>
-      </x:c>
+      <x:c r="M15"/>
       <x:c r="N15"/>
       <x:c r="O15"/>
       <x:c r="P15"/>
@@ -945,33 +825,23 @@
         <x:v>RainStorm</x:v>
       </x:c>
       <x:c r="D16" t="str">
-        <x:v>巫山云雨</x:v>
+        <x:v>boss</x:v>
       </x:c>
       <x:c r="E16" t="str">
-        <x:v>boss</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F16" t="str">
-        <x:v>战场下雨，降低所有单位攻速，升级可驱除</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="G16" t="str">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="H16" t="str">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="I16" t="str">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="J16" t="str">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="K16" t="str">
-        <x:v>12086</x:v>
-      </x:c>
+        <x:v>RainStorm</x:v>
+      </x:c>
+      <x:c r="H16"/>
+      <x:c r="I16"/>
+      <x:c r="J16"/>
+      <x:c r="K16"/>
       <x:c r="L16"/>
-      <x:c r="M16" t="str">
-        <x:v>RainStorm</x:v>
-      </x:c>
+      <x:c r="M16"/>
       <x:c r="N16"/>
       <x:c r="O16"/>
       <x:c r="P16"/>
@@ -986,35 +856,23 @@
         <x:v>Enthrall</x:v>
       </x:c>
       <x:c r="D17" t="str">
-        <x:v>裙下之臣</x:v>
+        <x:v>boss</x:v>
       </x:c>
       <x:c r="E17" t="str">
-        <x:v>boss</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F17" t="str">
-        <x:v>将最低等级的小兵纳入麾下</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="G17" t="str">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="H17" t="str">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="I17" t="str">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="J17" t="str">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="K17" t="str">
-        <x:v>12094</x:v>
-      </x:c>
-      <x:c r="L17" t="str">
-        <x:v>INFERRED_HEALTH_MULTIPLIER</x:v>
-      </x:c>
-      <x:c r="M17" t="str">
         <x:v>Enthrall</x:v>
       </x:c>
+      <x:c r="H17"/>
+      <x:c r="I17"/>
+      <x:c r="J17"/>
+      <x:c r="K17"/>
+      <x:c r="L17"/>
+      <x:c r="M17"/>
       <x:c r="N17"/>
       <x:c r="O17"/>
       <x:c r="P17"/>
@@ -1029,33 +887,23 @@
         <x:v>CavalryOrder</x:v>
       </x:c>
       <x:c r="D18" t="str">
-        <x:v>铁骑号令</x:v>
+        <x:v>boss</x:v>
       </x:c>
       <x:c r="E18" t="str">
-        <x:v>boss</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F18" t="str">
-        <x:v>召唤西凉骑兵</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="G18" t="str">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="H18" t="str">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="I18" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J18" t="str">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="K18" t="str">
-        <x:v>12102</x:v>
-      </x:c>
+        <x:v>CavalryOrder</x:v>
+      </x:c>
+      <x:c r="H18"/>
+      <x:c r="I18"/>
+      <x:c r="J18"/>
+      <x:c r="K18"/>
       <x:c r="L18"/>
-      <x:c r="M18" t="str">
-        <x:v>CavalryOrder</x:v>
-      </x:c>
+      <x:c r="M18"/>
       <x:c r="N18"/>
       <x:c r="O18"/>
       <x:c r="P18"/>
@@ -1070,33 +918,23 @@
         <x:v>FangTianHalberd</x:v>
       </x:c>
       <x:c r="D19" t="str">
-        <x:v>方天画戟</x:v>
+        <x:v>boss</x:v>
       </x:c>
       <x:c r="E19" t="str">
-        <x:v>boss</x:v>
+        <x:v>2.5</x:v>
       </x:c>
       <x:c r="F19" t="str">
-        <x:v>挥动武器，大幅降低小兵等级并禁止合成</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="G19" t="str">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="H19" t="str">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="I19" t="str">
-        <x:v>2.5</x:v>
-      </x:c>
-      <x:c r="J19" t="str">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="K19" t="str">
-        <x:v>12110</x:v>
-      </x:c>
+        <x:v>FangTianHalberd</x:v>
+      </x:c>
+      <x:c r="H19"/>
+      <x:c r="I19"/>
+      <x:c r="J19"/>
+      <x:c r="K19"/>
       <x:c r="L19"/>
-      <x:c r="M19" t="str">
-        <x:v>FangTianHalberd</x:v>
-      </x:c>
+      <x:c r="M19"/>
       <x:c r="N19"/>
       <x:c r="O19"/>
       <x:c r="P19"/>
@@ -1111,35 +949,23 @@
         <x:v>Devour</x:v>
       </x:c>
       <x:c r="D20" t="str">
-        <x:v>饕餮</x:v>
+        <x:v>boss</x:v>
       </x:c>
       <x:c r="E20" t="str">
-        <x:v>boss</x:v>
+        <x:v>1.5</x:v>
       </x:c>
       <x:c r="F20" t="str">
-        <x:v>吞噬范围内小兵，获得血量加成并膨胀</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="G20" t="str">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="H20" t="str">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="I20" t="str">
-        <x:v>1.5</x:v>
-      </x:c>
-      <x:c r="J20" t="str">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="K20" t="str">
-        <x:v>12118</x:v>
-      </x:c>
-      <x:c r="L20" t="str">
-        <x:v>INFERRED_HEALTH_MULTIPLIER</x:v>
-      </x:c>
-      <x:c r="M20" t="str">
         <x:v>Devour</x:v>
       </x:c>
+      <x:c r="H20"/>
+      <x:c r="I20"/>
+      <x:c r="J20"/>
+      <x:c r="K20"/>
+      <x:c r="L20"/>
+      <x:c r="M20"/>
       <x:c r="N20"/>
       <x:c r="O20"/>
       <x:c r="P20"/>
@@ -1154,35 +980,23 @@
         <x:v>Madness</x:v>
       </x:c>
       <x:c r="D21" t="str">
-        <x:v>彻底疯狂</x:v>
+        <x:v>boss</x:v>
       </x:c>
       <x:c r="E21" t="str">
-        <x:v>boss</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F21" t="str">
-        <x:v>冲阵击倒小兵，使其无法动弹，升级解除</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="G21" t="str">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="H21" t="str">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="I21" t="str">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="J21" t="str">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="K21" t="str">
-        <x:v>12126</x:v>
-      </x:c>
-      <x:c r="L21" t="str">
-        <x:v>INFERRED_COOLDOWN</x:v>
-      </x:c>
-      <x:c r="M21" t="str">
         <x:v>Madness</x:v>
       </x:c>
+      <x:c r="H21"/>
+      <x:c r="I21"/>
+      <x:c r="J21"/>
+      <x:c r="K21"/>
+      <x:c r="L21"/>
+      <x:c r="M21"/>
       <x:c r="N21"/>
       <x:c r="O21"/>
       <x:c r="P21"/>
@@ -1197,33 +1011,23 @@
         <x:v>DevourEyes</x:v>
       </x:c>
       <x:c r="D22" t="str">
-        <x:v>噬目</x:v>
+        <x:v>boss</x:v>
       </x:c>
       <x:c r="E22" t="str">
-        <x:v>boss</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F22" t="str">
-        <x:v>视野变暗，难以看清局势</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="G22" t="str">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="H22" t="str">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="I22" t="str">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="J22" t="str">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="K22" t="str">
-        <x:v>12134</x:v>
-      </x:c>
+        <x:v>DevourEyes</x:v>
+      </x:c>
+      <x:c r="H22"/>
+      <x:c r="I22"/>
+      <x:c r="J22"/>
+      <x:c r="K22"/>
       <x:c r="L22"/>
-      <x:c r="M22" t="str">
-        <x:v>DevourEyes</x:v>
-      </x:c>
+      <x:c r="M22"/>
       <x:c r="N22"/>
       <x:c r="O22"/>
       <x:c r="P22"/>
@@ -1238,35 +1042,23 @@
         <x:v>WarlordSeal</x:v>
       </x:c>
       <x:c r="D23" t="str">
-        <x:v>一代枭雄</x:v>
+        <x:v>boss</x:v>
       </x:c>
       <x:c r="E23" t="str">
-        <x:v>boss</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F23" t="str">
-        <x:v>封印最高等级小兵，升级解除</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="G23" t="str">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="H23" t="str">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="I23" t="str">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="J23" t="str">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="K23" t="str">
-        <x:v>12142</x:v>
-      </x:c>
-      <x:c r="L23" t="str">
-        <x:v>INFERRED_HEALTH_AND_COOLDOWN</x:v>
-      </x:c>
-      <x:c r="M23" t="str">
         <x:v>WarlordSeal</x:v>
       </x:c>
+      <x:c r="H23"/>
+      <x:c r="I23"/>
+      <x:c r="J23"/>
+      <x:c r="K23"/>
+      <x:c r="L23"/>
+      <x:c r="M23"/>
       <x:c r="N23"/>
       <x:c r="O23"/>
       <x:c r="P23"/>
